--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="217">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,7 +475,10 @@
     <t>food | medication | environment | biologic</t>
   </si>
   <si>
-    <t xml:space="preserve"> jdv-hl7-allergy-intolerance-category-cisis (2.16.840.1.113883.4.642.3.133)</t>
+    <t>jdv-hl7-allergy-intolerance-category-cisis (2.16.840.1.113883.4.642.3.133)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-allergy-intolerance-category-cisis|20260619134041</t>
   </si>
   <si>
     <t>fr-lm-allergy-intolerance.agentOrAllergen</t>
@@ -1017,7 +1020,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="60.30078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="59.80078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="84.5" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3107,7 +3110,7 @@
         <v>149</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3142,10 +3145,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3171,10 +3174,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3225,7 +3228,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3242,10 +3245,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3268,13 +3271,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3325,7 +3328,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3342,10 +3345,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3371,10 +3374,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3404,10 +3407,10 @@
         <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -3425,7 +3428,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3442,10 +3445,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3471,10 +3474,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3504,10 +3507,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3525,7 +3528,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3542,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3568,13 +3571,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3625,7 +3628,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3637,15 +3640,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3668,13 +3671,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3725,7 +3728,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3742,14 +3745,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -3768,16 +3771,16 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3815,19 +3818,19 @@
         <v>73</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3839,15 +3842,15 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3870,16 +3873,16 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3929,7 +3932,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -3946,10 +3949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3972,13 +3975,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4029,7 +4032,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4041,15 +4044,15 @@
         <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4075,10 +4078,10 @@
         <v>127</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4129,7 +4132,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4146,10 +4149,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4175,10 +4178,10 @@
         <v>127</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4229,7 +4232,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4246,10 +4249,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4275,10 +4278,10 @@
         <v>80</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4329,7 +4332,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4346,10 +4349,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4375,10 +4378,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4408,7 +4411,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4429,7 +4432,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4446,10 +4449,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4475,10 +4478,10 @@
         <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4508,7 +4511,7 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4529,7 +4532,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4546,10 +4549,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4575,10 +4578,10 @@
         <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4608,10 +4611,10 @@
         <v>73</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -4629,7 +4632,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4646,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4672,13 +4675,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4729,7 +4732,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -4741,15 +4744,15 @@
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4772,13 +4775,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4829,7 +4832,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4846,14 +4849,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -4872,16 +4875,16 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -4919,19 +4922,19 @@
         <v>73</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4943,15 +4946,15 @@
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4974,16 +4977,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5033,7 +5036,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -5050,10 +5053,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5076,13 +5079,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5133,7 +5136,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5145,15 +5148,15 @@
         <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5179,10 +5182,10 @@
         <v>127</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5233,7 +5236,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5250,10 +5253,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5279,10 +5282,10 @@
         <v>127</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5333,7 +5336,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="219">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>Statut</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-hl7-allergyintolerance-clinical-cisis (2.16.840.1.113883.4.642.3.1372)</t>
@@ -665,6 +668,9 @@
   </si>
   <si>
     <t>Sévérité de la manifestion</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>SNOMED_CT (preferred)</t>
@@ -2704,13 +2710,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2728,7 +2734,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2745,10 +2751,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2774,10 +2780,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2828,7 +2834,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2845,10 +2851,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2874,10 +2880,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2928,7 +2934,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2945,10 +2951,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2974,10 +2980,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3004,13 +3010,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3028,7 +3034,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3045,10 +3051,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3074,10 +3080,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3104,13 +3110,13 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3128,7 +3134,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3145,10 +3151,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3174,10 +3180,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3228,7 +3234,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3245,10 +3251,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3271,13 +3277,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3328,7 +3334,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3345,10 +3351,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3374,10 +3380,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3404,13 +3410,13 @@
         <v>73</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -3428,7 +3434,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3445,10 +3451,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3474,10 +3480,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3504,13 +3510,13 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3528,7 +3534,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3545,10 +3551,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3571,13 +3577,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3628,7 +3634,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3640,15 +3646,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3671,13 +3677,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3728,7 +3734,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3745,14 +3751,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -3771,16 +3777,16 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3818,19 +3824,19 @@
         <v>73</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3842,15 +3848,15 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3873,16 +3879,16 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3932,7 +3938,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -3949,10 +3955,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3975,13 +3981,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4032,7 +4038,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4044,15 +4050,15 @@
         <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4078,10 +4084,10 @@
         <v>127</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4132,7 +4138,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4149,10 +4155,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4178,10 +4184,10 @@
         <v>127</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4232,7 +4238,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4249,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4278,10 +4284,10 @@
         <v>80</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4332,7 +4338,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4349,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4378,10 +4384,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4408,10 +4414,10 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4432,7 +4438,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4449,10 +4455,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4478,10 +4484,10 @@
         <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4508,10 +4514,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4532,7 +4538,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4549,10 +4555,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4578,10 +4584,10 @@
         <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4608,13 +4614,13 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -4632,7 +4638,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4649,10 +4655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4675,13 +4681,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4732,7 +4738,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -4744,15 +4750,15 @@
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4775,13 +4781,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4832,7 +4838,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4849,14 +4855,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -4875,16 +4881,16 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -4922,19 +4928,19 @@
         <v>73</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4946,15 +4952,15 @@
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4977,16 +4983,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5036,7 +5042,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -5053,10 +5059,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5079,13 +5085,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5136,7 +5142,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5148,15 +5154,15 @@
         <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5182,10 +5188,10 @@
         <v>127</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5236,7 +5242,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5253,10 +5259,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5282,10 +5288,10 @@
         <v>127</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5336,7 +5342,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
